--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 1구역 이벤트 전투 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 1구역 이벤트 전투 테이블.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GA7thFinal_Orora\2_Documents\데이터 테이블\베타 밸런스\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264A751C-F137-405E-B993-ACF681535FA8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -19,8 +13,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1608,7 +1602,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -1638,7 +1632,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1694,7 +1688,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -1724,7 +1718,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1780,7 +1774,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -1810,7 +1804,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1866,7 +1860,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -1896,7 +1890,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1952,7 +1946,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -1982,7 +1976,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2038,7 +2032,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2057,7 +2051,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2113,7 +2107,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2132,7 +2126,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -2188,7 +2182,7 @@
           <a:schemeClr val="lt1"/>
         </a:fontRef>
       </xdr:style>
-      <xdr:txBody>
+      <a:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
@@ -2218,7 +2212,7 @@
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
+      </a:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -5662,7 +5656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A705E06-4C8A-43EB-9784-7D906D56BEF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Q39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5680,7 +5674,6 @@
     <col min="14" max="14" width="8.83203125" style="14" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.75" style="14" bestFit="1" customWidth="1"/>
     <col min="16" max="38" width="15.58203125" style="14" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
@@ -5812,28 +5805,28 @@
         <v>225</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="E6" s="16">
         <v>4</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G6" s="16">
         <v>6</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="I6" s="16">
         <v>3</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K6" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="49" t="s">
         <v>241</v>
@@ -5841,8 +5834,12 @@
       <c r="M6" s="16">
         <v>5</v>
       </c>
-      <c r="N6" s="49"/>
-      <c r="O6" s="16"/>
+      <c r="N6" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0</v>
+      </c>
       <c r="P6" s="16">
         <v>3</v>
       </c>
@@ -5858,28 +5855,28 @@
         <v>225</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="E7" s="16">
         <v>4</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G7" s="16">
         <v>6</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="I7" s="16">
         <v>3</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K7" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="49" t="s">
         <v>241</v>
@@ -5887,8 +5884,12 @@
       <c r="M7" s="16">
         <v>5</v>
       </c>
-      <c r="N7" s="49"/>
-      <c r="O7" s="16"/>
+      <c r="N7" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0</v>
+      </c>
       <c r="P7" s="16">
         <v>3</v>
       </c>
@@ -5904,28 +5905,28 @@
         <v>225</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="E8" s="16">
         <v>4</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G8" s="16">
         <v>6</v>
       </c>
       <c r="H8" s="49" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="I8" s="16">
         <v>3</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K8" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="49" t="s">
         <v>241</v>
@@ -5933,8 +5934,12 @@
       <c r="M8" s="16">
         <v>5</v>
       </c>
-      <c r="N8" s="49"/>
-      <c r="O8" s="16"/>
+      <c r="N8" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0</v>
+      </c>
       <c r="P8" s="16">
         <v>3</v>
       </c>
@@ -5950,33 +5955,41 @@
         <v>146</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="E9" s="16">
         <v>1</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G9" s="16">
         <v>3</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="I9" s="16">
         <v>4</v>
       </c>
       <c r="J9" s="50" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K9" s="16">
         <v>6</v>
       </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
+      <c r="L9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="O9" s="16">
+        <v>0</v>
+      </c>
       <c r="P9" s="16">
         <v>1</v>
       </c>
@@ -5992,33 +6005,41 @@
         <v>145</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="E10" s="16">
         <v>1</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G10" s="16">
         <v>3</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="I10" s="16">
         <v>5</v>
       </c>
       <c r="J10" s="50" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K10" s="16">
         <v>2</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="L10" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="O10" s="16">
+        <v>0</v>
+      </c>
       <c r="P10" s="16">
         <v>1</v>
       </c>
@@ -6034,33 +6055,41 @@
         <v>147</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="E11" s="16">
         <v>5</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="G11" s="16">
         <v>1</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="I11" s="16">
         <v>2</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K11" s="16">
         <v>3</v>
       </c>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
+      <c r="L11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0</v>
+      </c>
       <c r="P11" s="16">
         <v>2</v>
       </c>
@@ -6076,33 +6105,41 @@
         <v>148</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>233</v>
+        <v>98</v>
       </c>
       <c r="E12" s="16">
         <v>4</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="G12" s="16">
         <v>6</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="I12" s="16">
         <v>1</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K12" s="16">
         <v>3</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
+      <c r="L12" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" s="16">
+        <v>0</v>
+      </c>
       <c r="P12" s="16">
         <v>2</v>
       </c>
@@ -6118,37 +6155,41 @@
         <v>149</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="E13" s="16">
         <v>1</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G13" s="16">
         <v>3</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="I13" s="16">
         <v>4</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>230</v>
+        <v>98</v>
       </c>
       <c r="K13" s="16">
         <v>6</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="M13" s="16">
         <v>2</v>
       </c>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="N13" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
       <c r="P13" s="16">
         <v>2</v>
       </c>
@@ -6164,33 +6205,41 @@
         <v>231</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="E14" s="16">
         <v>6</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="G14" s="16">
         <v>1</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="I14" s="16">
         <v>2</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="K14" s="16">
         <v>5</v>
       </c>
-      <c r="L14" s="49"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="16"/>
+      <c r="L14" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="M14" s="16">
+        <v>0</v>
+      </c>
+      <c r="N14" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O14" s="16">
+        <v>0</v>
+      </c>
       <c r="P14" s="16">
         <v>2</v>
       </c>
@@ -6206,29 +6255,41 @@
         <v>177</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="E15" s="16">
         <v>1</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="G15" s="16">
         <v>2</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>232</v>
+        <v>99</v>
       </c>
       <c r="I15" s="16">
+        <v>3</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="K15" s="16">
         <v>5</v>
       </c>
-      <c r="J15" s="49"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="16"/>
+      <c r="L15" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O15" s="16">
+        <v>0</v>
+      </c>
       <c r="P15" s="16">
         <v>2</v>
       </c>
@@ -6244,21 +6305,41 @@
         <v>143</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E16" s="16">
         <v>2</v>
       </c>
-      <c r="F16" s="49"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="16"/>
+      <c r="F16" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="K16" s="16">
+        <v>0</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="O16" s="16">
+        <v>0</v>
+      </c>
       <c r="P16" s="16">
         <v>2</v>
       </c>
